--- a/Data/Rules/Front Porch Pets Rules Matrix.xlsx
+++ b/Data/Rules/Front Porch Pets Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>15694</t>
@@ -480,10 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AO3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -604,16 +607,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -658,10 +664,10 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -726,16 +732,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>67</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -780,10 +789,10 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -847,6 +856,9 @@
       </c>
       <c r="AN3">
         <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
